--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484032_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484032_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4231</v>
+        <v>4.0149</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7011</v>
+        <v>2.2929</v>
       </c>
       <c r="F2" t="n">
         <v>1.722</v>
@@ -610,10 +610,10 @@
         <v>2.1822</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2721</v>
+        <v>-0.136</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2382</v>
+        <v>-0.1699</v>
       </c>
       <c r="U2" t="n">
         <v>0.0339</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9126</v>
+        <v>1.41</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.5066</v>
+        <v>-0.5884</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4192</v>
+        <v>1.9984</v>
       </c>
       <c r="G3" t="n">
         <v>0.6645</v>
@@ -688,13 +688,13 @@
         <v>3.3725</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9665</v>
+        <v>-0.4691</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5586</v>
+        <v>-0.6404</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5921</v>
+        <v>0.1713</v>
       </c>
       <c r="V3" t="n">
         <v>1.8097</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ROSA BEJARANO</t>
+          <t>A. GARCIA MARTINEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0641</v>
+        <v>0.6044</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4294</v>
+        <v>0.2611</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4935</v>
+        <v>0.3433</v>
       </c>
       <c r="G4" t="n">
-        <v>1.398</v>
+        <v>0.5658</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9332</v>
+        <v>-0.2077</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5352</v>
+        <v>0.7735</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8982</v>
+        <v>1.9727</v>
       </c>
       <c r="K4" t="n">
-        <v>4.0578</v>
+        <v>0.5645</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1596</v>
+        <v>1.4082</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5002</v>
+        <v>-1.407</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1246</v>
+        <v>-0.7723</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3756</v>
+        <v>-0.6347</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7935</v>
+        <v>1.5871</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1822</v>
+        <v>2.579</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2006</v>
+        <v>-0.9452</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3005</v>
+        <v>-0.7197</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0999</v>
+        <v>-0.2255</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.8692</v>
+        <v>-0.6032</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.0757</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GARCIA MARTINEZ</t>
+          <t>A. ROSA BEJARANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1378</v>
+        <v>-0.8089</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4531</v>
+        <v>1.0213</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3153</v>
+        <v>-1.8302</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5658</v>
+        <v>1.398</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2077</v>
+        <v>2.9332</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7735</v>
+        <v>-1.5352</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9727</v>
+        <v>2.8982</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5645</v>
+        <v>4.0578</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4082</v>
+        <v>-1.1596</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.407</v>
+        <v>-1.5002</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7723</v>
+        <v>-1.1246</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6347</v>
+        <v>-0.3756</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5871</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R5" t="n">
-        <v>2.579</v>
+        <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6875</v>
+        <v>-0.5442</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4339</v>
+        <v>-0.1076</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2535</v>
+        <v>-0.4366</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6032</v>
+        <v>-0.8692</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6032</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>I. OLLE GATELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9897</v>
+        <v>-1.1369</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8915</v>
+        <v>-2.008</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9019</v>
+        <v>0.8711</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7644</v>
+        <v>0.9216</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4962</v>
+        <v>0.2971</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2681</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6446</v>
+        <v>0.1005</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.7651</v>
+        <v>0.0202</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1205</v>
+        <v>0.0803</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1197</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7311</v>
+        <v>0.277</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3886</v>
+        <v>0.5442</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1984</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7855</v>
+        <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2391</v>
+        <v>-0.4039</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7369</v>
+        <v>-0.1247</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5021</v>
+        <v>-0.2792</v>
       </c>
       <c r="V6" t="n">
         <v>-0.266</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. OLLE GATELL</t>
+          <t>G. GUTIÉRREZ MONREAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2211</v>
+        <v>-1.4984</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.008</v>
+        <v>-1.4528</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7869</v>
+        <v>-0.0456</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9216</v>
+        <v>-1.1895</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2971</v>
+        <v>0.4429</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6245000000000001</v>
+        <v>-1.6325</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1005</v>
+        <v>0.7188</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0202</v>
+        <v>1.4315</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0803</v>
+        <v>-0.7127</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8211000000000001</v>
+        <v>-1.9083</v>
       </c>
       <c r="N7" t="n">
-        <v>0.277</v>
+        <v>-0.9885</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5442</v>
+        <v>-0.9198</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3887</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5952</v>
+        <v>2.3806</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.488</v>
+        <v>-0.3882</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1247</v>
+        <v>-0.4023</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3634</v>
+        <v>0.0141</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.266</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GUTIÉRREZ MONREAL</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4627</v>
+        <v>-1.9283</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2488</v>
+        <v>-2.6057</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2139</v>
+        <v>0.6774</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1895</v>
+        <v>-1.7644</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4429</v>
+        <v>-1.4962</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6325</v>
+        <v>-0.2681</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7188</v>
+        <v>-0.6446</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4315</v>
+        <v>-0.7651</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7127</v>
+        <v>0.1205</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9083</v>
+        <v>-1.1197</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9885</v>
+        <v>-0.7311</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9198</v>
+        <v>-0.3886</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>2.3806</v>
+        <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3525</v>
+        <v>0.3004</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1982</v>
+        <v>0.0227</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1543</v>
+        <v>0.2777</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6745</v>
+        <v>-0.266</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.532</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.053</v>
+        <v>-1.9358</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6344</v>
+        <v>-3.0222</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5814</v>
+        <v>1.0864</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8366</v>
@@ -1156,13 +1156,13 @@
         <v>2.9758</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.2083</v>
+        <v>-1.0911</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3092</v>
+        <v>-0.6971000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.899</v>
+        <v>-0.394</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3567</v>
+        <v>-4.6705</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.4457</v>
+        <v>-5.9559</v>
       </c>
       <c r="F10" t="n">
-        <v>1.089</v>
+        <v>1.2854</v>
       </c>
       <c r="G10" t="n">
         <v>-2.7958</v>
@@ -1234,13 +1234,13 @@
         <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0334</v>
+        <v>-0.3472</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1758</v>
+        <v>-0.3343</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2092</v>
+        <v>-0.0129</v>
       </c>
       <c r="V10" t="n">
         <v>-0.3373</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9494</v>
+        <v>-5.9495</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.0576</v>
+        <v>-12.0577</v>
       </c>
       <c r="F11" t="n">
-        <v>6.1083</v>
+        <v>6.108199999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0162</v>
@@ -1294,7 +1294,7 @@
         <v>-0.9404000000000002</v>
       </c>
       <c r="M11" t="n">
-        <v>-8.338199999999999</v>
+        <v>-8.338200000000001</v>
       </c>
       <c r="N11" t="n">
         <v>-4.517</v>
@@ -1312,13 +1312,13 @@
         <v>19.8385</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.0244</v>
+        <v>-4.0245</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.1732</v>
+        <v>-3.1733</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.8512000000000002</v>
+        <v>-0.8512000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>1.083</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. POU BLINNIKOV</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.0526</v>
+        <v>5.6886</v>
       </c>
       <c r="E12" t="n">
-        <v>6.0503</v>
+        <v>1.7973</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0022</v>
+        <v>3.8913</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6961</v>
+        <v>2.2395</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3538</v>
+        <v>1.83</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3423</v>
+        <v>0.4095</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3194</v>
+        <v>2.3186</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8735</v>
+        <v>2.0777</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4458</v>
+        <v>0.241</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.6233</v>
+        <v>-0.0791</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.2477</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1035</v>
+        <v>0.1685</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.5952</v>
+        <v>2.579</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1741</v>
+        <v>-0.1984</v>
       </c>
       <c r="R12" t="n">
-        <v>2.579</v>
+        <v>2.7774</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8208</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>4.0359</v>
+        <v>-0.323</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7849</v>
+        <v>0.8557</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8692</v>
+        <v>0.3373</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7384</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>M. GARCIA CALVO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.168</v>
+        <v>5.193</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4912</v>
+        <v>2.003</v>
       </c>
       <c r="F13" t="n">
-        <v>4.6768</v>
+        <v>3.1901</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2395</v>
+        <v>3.8793</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83</v>
+        <v>1.0991</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4095</v>
+        <v>2.7802</v>
       </c>
       <c r="J13" t="n">
-        <v>2.3186</v>
+        <v>4.1552</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0777</v>
+        <v>1.8156</v>
       </c>
       <c r="L13" t="n">
-        <v>0.241</v>
+        <v>2.3396</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0791</v>
+        <v>-0.2758</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2477</v>
+        <v>-0.7165</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1685</v>
+        <v>0.4406</v>
       </c>
       <c r="P13" t="n">
+        <v>-0.5952</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-3.1741</v>
+      </c>
+      <c r="R13" t="n">
         <v>2.579</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-0.1984</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.7774</v>
-      </c>
       <c r="S13" t="n">
-        <v>1.0122</v>
+        <v>0.7737000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6291</v>
+        <v>-0.1132</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6413</v>
+        <v>0.8869</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3373</v>
+        <v>1.1352</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.1352</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3373</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. GARCIA CALVO</t>
+          <t>A. POU BLINNIKOV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6878</v>
+        <v>4.4636</v>
       </c>
       <c r="E14" t="n">
-        <v>2.105</v>
+        <v>3.6016</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5828</v>
+        <v>0.8619</v>
       </c>
       <c r="G14" t="n">
-        <v>3.8793</v>
+        <v>3.6961</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0991</v>
+        <v>2.3538</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7802</v>
+        <v>1.3423</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1552</v>
+        <v>4.3194</v>
       </c>
       <c r="K14" t="n">
-        <v>1.8156</v>
+        <v>2.8735</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3396</v>
+        <v>1.4458</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2758</v>
+        <v>-0.6233</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7165</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4406</v>
+        <v>-0.1035</v>
       </c>
       <c r="P14" t="n">
         <v>-0.5952</v>
@@ -1546,22 +1546,22 @@
         <v>2.579</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2685</v>
+        <v>2.2319</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0112</v>
+        <v>1.5872</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2797</v>
+        <v>0.6446</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1352</v>
+        <v>-0.8692</v>
       </c>
       <c r="W14" t="n">
-        <v>1.1352</v>
+        <v>0.8692</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7746</v>
+        <v>3.1954</v>
       </c>
       <c r="E15" t="n">
         <v>1.5546</v>
       </c>
       <c r="F15" t="n">
-        <v>1.22</v>
+        <v>1.6408</v>
       </c>
       <c r="G15" t="n">
         <v>0.3074</v>
@@ -1624,13 +1624,13 @@
         <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7907</v>
+        <v>-0.3698</v>
       </c>
       <c r="T15" t="n">
         <v>-0.255</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5357</v>
+        <v>-0.1149</v>
       </c>
       <c r="V15" t="n">
         <v>1.4724</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. BRADLEY MAYOL</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.85</v>
+        <v>0.222</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9094</v>
+        <v>1.2635</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0594</v>
+        <v>-1.0415</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8551</v>
+        <v>0.0361</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8616</v>
+        <v>0.5998</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0065</v>
+        <v>-0.5637</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.66</v>
+        <v>1.1331</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.66</v>
+        <v>1.3211</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.188</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1951</v>
+        <v>-1.097</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2016</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0065</v>
+        <v>-0.3756</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1984</v>
+        <v>2.579</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1984</v>
+        <v>2.579</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1933</v>
+        <v>0.0199</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2494</v>
+        <v>0.1305</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0561</v>
+        <v>-0.1106</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-2.4129</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>A. MONTALBÁN PÉREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2012</v>
+        <v>-0.0118</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3453</v>
+        <v>-3.0031</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5465</v>
+        <v>2.9913</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0361</v>
+        <v>-2.3459</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5998</v>
+        <v>-2.263</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5637</v>
+        <v>-0.0829</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1331</v>
+        <v>-1.9931</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3211</v>
+        <v>-0.7959000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.188</v>
+        <v>-1.1972</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.097</v>
+        <v>-0.3528</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-1.4671</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3756</v>
+        <v>1.1143</v>
       </c>
       <c r="P17" t="n">
-        <v>2.579</v>
+        <v>0.7935</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.1822</v>
       </c>
       <c r="R17" t="n">
-        <v>2.579</v>
+        <v>2.9758</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4034</v>
+        <v>0.7425</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7877999999999999</v>
+        <v>0.3742</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6156</v>
+        <v>0.3683</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.4129</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. IDDRISU</t>
+          <t>J. BRADLEY MAYOL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5293</v>
+        <v>-0.7659</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7614</v>
+        <v>-0.9094</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7679</v>
+        <v>0.1435</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3719</v>
+        <v>-0.8551</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4081</v>
+        <v>-0.8616</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0362</v>
+        <v>0.0065</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6933</v>
+        <v>-0.66</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6129</v>
+        <v>-0.66</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0803</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3213</v>
+        <v>-0.1951</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2048</v>
+        <v>-0.2016</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1165</v>
+        <v>0.0065</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7855</v>
+        <v>0.1984</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8247</v>
+        <v>-0.1091</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2551</v>
+        <v>-0.2494</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5696</v>
+        <v>0.1403</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9405</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MONTALBÁN PÉREZ</t>
+          <t>A. IDDRISU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5729</v>
+        <v>-1.8737</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.2275</v>
+        <v>-0.9655</v>
       </c>
       <c r="F19" t="n">
-        <v>2.6546</v>
+        <v>-0.9082</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3459</v>
+        <v>0.3719</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.263</v>
+        <v>0.4081</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0829</v>
+        <v>-0.0362</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9931</v>
+        <v>1.6933</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7959000000000001</v>
+        <v>1.6129</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1972</v>
+        <v>0.0803</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3528</v>
+        <v>-1.3213</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4671</v>
+        <v>-1.2048</v>
       </c>
       <c r="O19" t="n">
-        <v>1.1143</v>
+        <v>-0.1165</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7935</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1822</v>
+        <v>-2.9758</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9758</v>
+        <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8185</v>
+        <v>0.4804</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8501</v>
+        <v>0.0511</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0317</v>
+        <v>0.4293</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7979000000000001</v>
+        <v>-0.9405</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.266</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SANTANDREU RODRIGUEZ</t>
+          <t>B. MARTINEZ JANER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3594</v>
+        <v>-3.1047</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2749</v>
+        <v>-3.6046</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.4999</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5728</v>
+        <v>-1.7972</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5442</v>
+        <v>-1.5471</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0286</v>
+        <v>-0.25</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.917</v>
+        <v>-1.2921</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0402</v>
+        <v>-0.6776</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6558</v>
+        <v>-0.5051</v>
       </c>
       <c r="N20" t="n">
-        <v>0.413</v>
+        <v>-0.9327</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0688</v>
+        <v>0.4276</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3887</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5952</v>
+        <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3979</v>
+        <v>-0.5059</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3741</v>
+        <v>-0.3287</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0238</v>
+        <v>-0.1772</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>M. SANTANDREU RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5116</v>
+        <v>-3.191</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.4688</v>
+        <v>-3.2749</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.0839</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9432</v>
+        <v>-1.5728</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.013</v>
+        <v>-0.5442</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9302</v>
+        <v>-1.0286</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9546</v>
+        <v>-0.917</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.277</v>
+        <v>-0.9572000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6776</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9886</v>
+        <v>-0.6558</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.736</v>
+        <v>0.413</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2526</v>
+        <v>-1.0688</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.3806</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9677</v>
+        <v>-1.9838</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8122</v>
+        <v>-0.2296</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4535</v>
+        <v>-0.3741</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3587</v>
+        <v>0.1445</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. MARTINEZ JANER</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7092</v>
+        <v>-3.8661</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0127</v>
+        <v>-4.5708</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3035</v>
+        <v>0.7047</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7972</v>
+        <v>-1.9432</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5471</v>
+        <v>-1.013</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.25</v>
+        <v>-0.9302</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2921</v>
+        <v>-0.9546</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-0.277</v>
       </c>
       <c r="L22" t="n">
         <v>-0.6776</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5051</v>
+        <v>-0.9886</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9327</v>
+        <v>-0.736</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4276</v>
+        <v>-0.2526</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1984</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9838</v>
+        <v>-3.9677</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7855</v>
+        <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1104</v>
+        <v>0.4577</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7368</v>
+        <v>0.3515</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3736</v>
+        <v>0.1062</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.949400000000002</v>
+        <v>5.949399999999997</v>
       </c>
       <c r="E23" t="n">
         <v>-6.1083</v>
       </c>
       <c r="F23" t="n">
-        <v>12.0576</v>
+        <v>12.0577</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0161</v>
+        <v>2.016099999999999</v>
       </c>
       <c r="H23" t="n">
         <v>-2.7452</v>
@@ -2233,13 +2233,13 @@
         <v>-6.321999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.262199999999999</v>
+        <v>-7.2622</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9401999999999999</v>
+        <v>0.9402000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9918000000000003</v>
+        <v>0.9918</v>
       </c>
       <c r="Q23" t="n">
         <v>-19.8383</v>
@@ -2248,13 +2248,13 @@
         <v>20.8305</v>
       </c>
       <c r="S23" t="n">
-        <v>4.0242</v>
+        <v>4.024500000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8509999999999996</v>
+        <v>0.8510999999999997</v>
       </c>
       <c r="U23" t="n">
-        <v>3.1733</v>
+        <v>3.1731</v>
       </c>
       <c r="V23" t="n">
         <v>-1.083</v>
